--- a/TeamData.xlsx
+++ b/TeamData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TUONG VY\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="13_ncr:1_{456A9A39-3618-4040-BD3A-EAE113E2B10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11CE9032-3E2B-44C0-9EF9-20BC84323699}"/>
+  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{456A9A39-3618-4040-BD3A-EAE113E2B10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F12CF2D-6640-45A8-B0C6-63E7221D913B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MEMBERS" sheetId="1" r:id="rId1"/>
@@ -335,21 +335,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -367,36 +365,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -812,10 +780,10 @@
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
     <col min="2" max="2" width="55.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75">
@@ -945,33 +913,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:E6">
-    <cfRule type="expression" dxfId="7" priority="12">
+    <cfRule type="expression" dxfId="4" priority="12">
       <formula>AND($D2&lt;&gt;"Completed",$E2&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:E6">
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>$D2="Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:E6">
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>$D2="In progress"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D12:D14">
-    <cfRule type="expression" dxfId="4" priority="9">
-      <formula>AND(#REF!&lt;&gt;"Completed",$E12&lt;TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D12:D14">
-    <cfRule type="expression" dxfId="3" priority="8">
-      <formula>#REF!="Completed"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D12:D14">
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>#REF!="In progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1081,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B4830C-01A8-4ADF-8263-CD8E2E82CF6F}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -1093,301 +1046,300 @@
     <col min="7" max="7" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="15.75">
+      <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:7" ht="15.75">
+      <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="str">
+      <c r="F2" s="3" t="str">
         <f>VLOOKUP(B2, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Trần Thị Minh Thảo</v>
       </c>
-      <c r="G2" s="3" t="str">
+      <c r="G2" s="1" t="str">
         <f>VLOOKUP(A2, PROJECTS!A:B, 2, FALSE)</f>
         <v>Introduction to IT Project</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:7" ht="15.75">
+      <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="str">
+      <c r="F3" s="3" t="str">
         <f>VLOOKUP(B3, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Trần Thị Minh Thảo</v>
       </c>
-      <c r="G3" s="3" t="str">
+      <c r="G3" s="1" t="str">
         <f>VLOOKUP(A3, PROJECTS!A:B, 2, FALSE)</f>
         <v>Introduction to IT Project</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:7" ht="15.75">
+      <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="str">
+      <c r="F4" s="3" t="str">
         <f>VLOOKUP(B4, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Trần Thị Minh Thảo</v>
       </c>
-      <c r="G4" s="3" t="str">
+      <c r="G4" s="1" t="str">
         <f>VLOOKUP(A4, PROJECTS!A:B, 2, FALSE)</f>
         <v>Introduction to IT Project</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:7" ht="15.75">
+      <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="str">
+      <c r="F5" s="3" t="str">
         <f>VLOOKUP(B5, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Nguyễn Ngọc Tường Vy</v>
       </c>
-      <c r="G5" s="3" t="str">
+      <c r="G5" s="1" t="str">
         <f>VLOOKUP(A5, PROJECTS!A:B, 2, FALSE)</f>
         <v>Office Productivity (Excel/Word)</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:7" ht="15.75">
+      <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="str">
+      <c r="F6" s="3" t="str">
         <f>VLOOKUP(B6, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Nguyễn Ngọc Tường Vy</v>
       </c>
-      <c r="G6" s="3" t="str">
+      <c r="G6" s="1" t="str">
         <f>VLOOKUP(A6, PROJECTS!A:B, 2, FALSE)</f>
         <v>Office Productivity (Excel/Word)</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:7" ht="15.75">
+      <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="str">
+      <c r="F7" s="3" t="str">
         <f>VLOOKUP(B7, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Trần Thị Ngọc Huyền</v>
       </c>
-      <c r="G7" s="3" t="str">
+      <c r="G7" s="1" t="str">
         <f>VLOOKUP(A7, PROJECTS!A:B, 2, FALSE)</f>
         <v>Operating Systems &amp; Bash Script</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:7" ht="15.75">
+      <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="4" t="str">
+      <c r="F8" s="3" t="str">
         <f>VLOOKUP(B8, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Trần Thị Ngọc Huyền</v>
       </c>
-      <c r="G8" s="3" t="str">
+      <c r="G8" s="1" t="str">
         <f>VLOOKUP(A8, PROJECTS!A:B, 2, FALSE)</f>
         <v>Operating Systems &amp; Bash Script</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:7" ht="15.75">
+      <c r="A9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="str">
+      <c r="F9" s="3" t="str">
         <f>VLOOKUP(B9, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Đặng Bích Phương</v>
       </c>
-      <c r="G9" s="3" t="str">
+      <c r="G9" s="1" t="str">
         <f>VLOOKUP(A9, PROJECTS!A:B, 2, FALSE)</f>
         <v>Digital Security &amp; Infrastructure</v>
       </c>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="15.75">
+      <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="4" t="str">
+      <c r="F10" s="3" t="str">
         <f>VLOOKUP(B10, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Đặng Bích Phương</v>
       </c>
-      <c r="G10" s="3" t="str">
+      <c r="G10" s="1" t="str">
         <f>VLOOKUP(A10, PROJECTS!A:B, 2, FALSE)</f>
         <v>Digital Security &amp; Infrastructure</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:7" ht="15.75">
+      <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="str">
+      <c r="F11" s="3" t="str">
         <f>VLOOKUP(B11, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Tiêu Bùi Như Ý</v>
       </c>
-      <c r="G11" s="3" t="str">
+      <c r="G11" s="1" t="str">
         <f>VLOOKUP(A11, PROJECTS!A:B, 2, FALSE)</f>
         <v>Technical Reporting &amp; Video Production</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:7" ht="15.75">
+      <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="4" t="str">
+      <c r="F12" s="3" t="str">
         <f>VLOOKUP(B12, ASSIGNMENTS!A:F, 6, FALSE)</f>
         <v>Tiêu Bùi Như Ý</v>
       </c>
-      <c r="G12" s="3" t="str">
+      <c r="G12" s="1" t="str">
         <f>VLOOKUP(A12, PROJECTS!A:B, 2, FALSE)</f>
         <v>Technical Reporting &amp; Video Production</v>
       </c>

--- a/TeamData.xlsx
+++ b/TeamData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TUONG VY\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{456A9A39-3618-4040-BD3A-EAE113E2B10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F12CF2D-6640-45A8-B0C6-63E7221D913B}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="13_ncr:1_{456A9A39-3618-4040-BD3A-EAE113E2B10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA881135-DC49-46DA-A012-D2DED12E0C5D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MEMBERS" sheetId="1" r:id="rId1"/>
@@ -1056,10 +1056,10 @@
       <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>56</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1079,10 +1079,10 @@
       <c r="C2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="4">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="str">
@@ -1104,10 +1104,10 @@
       <c r="C3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="4">
         <v>1</v>
       </c>
       <c r="F3" s="3" t="str">
@@ -1129,10 +1129,10 @@
       <c r="C4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="4">
         <v>1</v>
       </c>
       <c r="F4" s="3" t="str">
@@ -1154,10 +1154,10 @@
       <c r="C5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="str">
@@ -1179,10 +1179,10 @@
       <c r="C6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="4">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="str">
@@ -1204,10 +1204,10 @@
       <c r="C7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="4">
         <v>1</v>
       </c>
       <c r="F7" s="3" t="str">
@@ -1229,10 +1229,10 @@
       <c r="C8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="4">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="str">
@@ -1254,10 +1254,10 @@
       <c r="C9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="4">
         <v>1</v>
       </c>
       <c r="F9" s="3" t="str">
@@ -1279,10 +1279,10 @@
       <c r="C10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="4">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="str">
@@ -1304,10 +1304,10 @@
       <c r="C11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="4">
         <v>1</v>
       </c>
       <c r="F11" s="3" t="str">
@@ -1329,10 +1329,10 @@
       <c r="C12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="4">
         <v>1</v>
       </c>
       <c r="F12" s="3" t="str">
